--- a/documents/Asset_Management_Templates.xlsx
+++ b/documents/Asset_Management_Templates.xlsx
@@ -10,8 +10,8 @@
   <sheets>
     <sheet name="asset_inventory" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="asset_types" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="asset_owners" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="asset_locations" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="asset_locations" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="asset_owners" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="asset_dependencies" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="asset_security_status" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="network_zones" sheetId="7" state="visible" r:id="rId9"/>
@@ -241,6 +241,75 @@
     <t xml:space="preserve">IDS/IPS/Proxy/Email/Web security</t>
   </si>
   <si>
+    <t xml:space="preserve">site_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rack_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">network_zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vlan_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rack-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0.0.0/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Management rack in DC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rack-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.168.20.0/24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HQ core rack</t>
+  </si>
+  <si>
     <t xml:space="preserve">full_name</t>
   </si>
   <si>
@@ -296,75 +365,6 @@
   </si>
   <si>
     <t xml:space="preserve">2025-11-09T08:12:17.259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">site_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rack_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">floor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">network_zone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vlan_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">subnet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rack-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Server Room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Management</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0.0.0/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Management rack in DC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rack-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core Room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.168.20.0/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HQ core rack</t>
   </si>
   <si>
     <t xml:space="preserve">depends_on_id</t>
@@ -515,7 +515,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -538,7 +537,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -590,28 +588,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -670,14 +664,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -685,58 +679,25 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -754,48 +715,12 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
@@ -810,170 +735,170 @@
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="23.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="14.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="35.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="41.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="37.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="12.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="17.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="14.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="18.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="35.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="41.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="37.31"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="O2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="P2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="Q2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="0" t="s">
+      <c r="R2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="0" t="s">
+      <c r="S2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="T2" s="0" t="n">
+      <c r="T2" s="1" t="n">
         <v>15000</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="U2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="V2" s="0" t="s">
+      <c r="V2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="W2" s="0" t="s">
+      <c r="W2" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -996,28 +921,28 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1040,28 +965,28 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1083,29 +1008,32 @@
   </sheetPr>
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.63"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1128,33 +1056,33 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>155</v>
       </c>
     </row>
@@ -1177,162 +1105,162 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="24.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="54.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54.2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1352,94 +1280,94 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="41.12"/>
-  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="H1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="G2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>87</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1458,93 +1386,93 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="35.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="41.12"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="E1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="H2" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>110</v>
       </c>
     </row>
@@ -1567,37 +1495,37 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1620,81 +1548,81 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="31.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="33.5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="b">
+      <c r="C2" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E2" s="5" t="b">
+      <c r="E2" s="4" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="5" t="b">
+      <c r="G2" s="4" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1716,34 +1644,37 @@
   </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.11"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>129</v>
       </c>
     </row>
@@ -1766,41 +1697,41 @@
   <dimension ref="A1:A7"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="54.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.34"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1822,44 +1753,47 @@
   </sheetPr>
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="57.87"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>142</v>
       </c>
     </row>

--- a/documents/Asset_Management_Templates.xlsx
+++ b/documents/Asset_Management_Templates.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="157">
   <si>
     <t xml:space="preserve">asset_id</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t xml:space="preserve">2025-11-09T08:12:17.256583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
   </si>
   <si>
     <t xml:space="preserve">id</t>
@@ -732,7 +735,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.25"/>
@@ -902,6 +905,11 @@
         <v>41</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="V15" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -923,22 +931,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -967,12 +975,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -982,7 +990,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1024,17 +1032,17 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -1058,32 +1066,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -1112,13 +1120,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>20</v>
@@ -1129,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1143,13 +1151,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1157,13 +1165,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1171,13 +1179,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1185,13 +1193,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1199,13 +1207,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1213,13 +1221,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1227,13 +1235,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1241,13 +1249,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1255,13 +1263,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1285,28 +1293,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>20</v>
@@ -1317,28 +1325,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1346,28 +1354,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1400,25 +1408,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>21</v>
@@ -1429,25 +1437,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1455,25 +1463,25 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1497,16 +1505,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>20</v>
@@ -1520,13 +1528,13 @@
         <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1561,34 +1569,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1603,7 +1611,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E2" s="4" t="b">
         <f aca="false">TRUE()</f>
@@ -1620,10 +1628,10 @@
         <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1650,32 +1658,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1707,32 +1715,32 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1767,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1769,32 +1777,32 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/documents/Asset_Management_Templates.xlsx
+++ b/documents/Asset_Management_Templates.xlsx
@@ -591,25 +591,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -761,76 +757,77 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="35.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="41.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="37.31"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="24" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -928,9 +925,13 @@
   </sheetPr>
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="15.77"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="8.59"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>144</v>
       </c>
     </row>
@@ -972,9 +973,13 @@
   </sheetPr>
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="15.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="8.59"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1017,11 +1022,12 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="31.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1063,13 +1069,17 @@
   </sheetPr>
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="38.47"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="8.59"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="28.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>115</v>
       </c>
@@ -1116,24 +1126,25 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="24.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54.2"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="8.59"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="29.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1147,7 +1158,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1161,7 +1172,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1175,7 +1186,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1189,7 +1200,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1203,7 +1214,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1217,7 +1228,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1231,7 +1242,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1245,7 +1256,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1259,7 +1270,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1290,33 +1301,45 @@
   </sheetPr>
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="17.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="18.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="20.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="23.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="32.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="35.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="8.59"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1400,35 +1423,37 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="28.46"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="35.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="30.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="41.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1502,21 +1527,29 @@
   </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="8.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="29.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="37.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="32.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="40.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="2" width="8.59"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1556,6 +1589,7 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="8.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28.05"/>
@@ -1565,37 +1599,38 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="33.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1613,18 +1648,18 @@
       <c r="D2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E2" s="4" t="b">
+      <c r="E2" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="4" t="b">
+      <c r="G2" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
@@ -1653,11 +1688,12 @@
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="50.11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1706,10 +1742,11 @@
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="54.34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1762,11 +1799,12 @@
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="57.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="57.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="2" width="8.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>137</v>
       </c>
     </row>
